--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.3691641770417</v>
+        <v>3.472489178769276</v>
       </c>
       <c r="D2" t="n">
-        <v>21.51541921965572</v>
+        <v>3.496255623194055</v>
       </c>
       <c r="E2" t="n">
-        <v>2.129918511552827</v>
+        <v>0.3461117581273343</v>
       </c>
       <c r="F2" t="n">
-        <v>2.010325200489325</v>
+        <v>0.3266778450795154</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.62900120014735</v>
+        <v>4.164712695023945</v>
       </c>
       <c r="D3" t="n">
-        <v>25.53606962063437</v>
+        <v>4.149611313353086</v>
       </c>
       <c r="E3" t="n">
-        <v>2.129918511552827</v>
+        <v>0.3461117581273343</v>
       </c>
       <c r="F3" t="n">
-        <v>2.010325200489325</v>
+        <v>0.3266778450795154</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
